--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -33,7 +33,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -43,6 +43,13 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
@@ -448,6 +455,7 @@
         <x:f>Sum(D3:D4)</x:f>
       </x:c>
       <x:c r="E5" s="0" t="s"/>
+      <x:c r="G5" s="0" t="s"/>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="B6" s="0" t="s"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -91,19 +91,19 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="2">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/ShiftingFormulas.xlsx
@@ -408,14 +408,9 @@
     <x:col min="1" max="2" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
-      <x:c r="B1" s="0" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:7">
-      <x:c r="B2" s="0" t="s"/>
-    </x:row>
+    <x:row r="1" spans="1:7"/>
+    <x:row r="2" spans="1:7"/>
     <x:row r="3" spans="1:7">
-      <x:c r="B3" s="0" t="s"/>
       <x:c r="C3" s="0" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -433,7 +428,6 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="B4" s="0" t="s"/>
       <x:c r="C4" s="0" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -454,12 +448,8 @@
       <x:c r="D5" s="0">
         <x:f>Sum(D3:D4)</x:f>
       </x:c>
-      <x:c r="E5" s="0" t="s"/>
-      <x:c r="G5" s="0" t="s"/>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="B6" s="0" t="s"/>
-    </x:row>
+    </x:row>
+    <x:row r="6" spans="1:7"/>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
